--- a/rules/CORE-000718/negative/01/data/unit-test-coreid-FB3209-negative.xlsx
+++ b/rules/CORE-000718/negative/01/data/unit-test-coreid-FB3209-negative.xlsx
@@ -57,6 +57,10 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <color rgb="FF000000"/>
     </font>
     <font>
@@ -77,11 +81,7 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
       <sz val="11"/>
@@ -166,10 +166,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -504,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B2"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="str">
@@ -515,24 +515,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="4" t="str">
         <v>sdtmig</v>
       </c>
-      <c r="B2" s="4" t="str">
+      <c r="B2" s="5" t="str">
         <v>3-4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="str">
-        <v/>
-      </c>
-      <c r="B3" s="4" t="str">
-        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -550,42 +542,42 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="4" t="str">
         <v>sm.xpt</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="4" t="str">
         <v>Subject Disease Milestones</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="str">
+      <c r="A3" s="4" t="str">
         <v>se.xpt</v>
       </c>
-      <c r="B3" s="2" t="str">
+      <c r="B3" s="4" t="str">
         <v>Subject Elements</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="str">
+      <c r="A4" s="4" t="str">
         <v>sv.xpt</v>
       </c>
-      <c r="B4" s="2" t="str">
+      <c r="B4" s="4" t="str">
         <v>Subject Visits</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="str">
+      <c r="A5" s="4" t="str">
         <v>ae.xpt</v>
       </c>
-      <c r="B5" s="2" t="str">
+      <c r="B5" s="4" t="str">
         <v>Adverse Events</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="str">
+      <c r="A6" s="4" t="str">
         <v>cm.xpt</v>
       </c>
-      <c r="B6" s="2" t="str">
+      <c r="B6" s="4" t="str">
         <v>Concomitant/Prior Medications</v>
       </c>
     </row>
@@ -621,202 +613,202 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="4" t="str">
         <v>sm.xpt</v>
       </c>
-      <c r="C2" s="2" t="str">
+      <c r="C2" s="4" t="str">
         <v>Record</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="4">
         <v>7</v>
       </c>
-      <c r="E2" s="2" t="str">
+      <c r="E2" s="4" t="str">
         <v>SMSTDTC</v>
       </c>
-      <c r="F2" s="2" t="str">
+      <c r="F2" s="4" t="str">
+        <v>2018-07-18T11:16</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="str">
+        <v>sm.xpt</v>
+      </c>
+      <c r="C3" s="4" t="str">
+        <v>Record</v>
+      </c>
+      <c r="D3" s="4">
+        <v>7</v>
+      </c>
+      <c r="E3" s="4" t="str">
+        <v>SMENDTC</v>
+      </c>
+      <c r="F3" s="4" t="str">
         <v>2018-07-18T11:15</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="str">
-        <v>sm.xpt</v>
-      </c>
-      <c r="C3" s="2" t="str">
+    <row r="4">
+      <c r="A4" s="4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="str">
+        <v>se.xpt</v>
+      </c>
+      <c r="C4" s="4" t="str">
         <v>Record</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D4" s="4">
+        <v>5</v>
+      </c>
+      <c r="E4" s="4" t="str">
+        <v>SESTDTC</v>
+      </c>
+      <c r="F4" s="4" t="str">
+        <v>2018-01-24</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="str">
+        <v>se.xpt</v>
+      </c>
+      <c r="C5" s="4" t="str">
+        <v>Record</v>
+      </c>
+      <c r="D5" s="4">
+        <v>5</v>
+      </c>
+      <c r="E5" s="4" t="str">
+        <v>SEENDTC</v>
+      </c>
+      <c r="F5" s="4" t="str">
+        <v>2006-03-10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="str">
+        <v>sv.xpt</v>
+      </c>
+      <c r="C6" s="4" t="str">
+        <v>Record</v>
+      </c>
+      <c r="D6" s="4">
+        <v>6</v>
+      </c>
+      <c r="E6" s="4" t="str">
+        <v>SVSTDTC</v>
+      </c>
+      <c r="F6" s="4" t="str">
+        <v>2018-02-20T16:38</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="str">
+        <v>sv.xpt</v>
+      </c>
+      <c r="C7" s="4" t="str">
+        <v>Record</v>
+      </c>
+      <c r="D7" s="4">
+        <v>6</v>
+      </c>
+      <c r="E7" s="4" t="str">
+        <v>SVENDTC</v>
+      </c>
+      <c r="F7" s="4" t="str">
+        <v>2018-02-20T16:31:00</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="str">
+        <v>ae.xpt</v>
+      </c>
+      <c r="C8" s="4" t="str">
+        <v>Record</v>
+      </c>
+      <c r="D8" s="4">
+        <v>12</v>
+      </c>
+      <c r="E8" s="4" t="str">
+        <v>AESTDTC</v>
+      </c>
+      <c r="F8" s="4">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4">
+        <v>4</v>
+      </c>
+      <c r="B9" s="4" t="str">
+        <v>ae.xpt</v>
+      </c>
+      <c r="C9" s="4" t="str">
+        <v>Record</v>
+      </c>
+      <c r="D9" s="4">
+        <v>12</v>
+      </c>
+      <c r="E9" s="4" t="str">
+        <v>AEENDTC</v>
+      </c>
+      <c r="F9" s="4" t="str">
+        <v>2018-06-14</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4">
+        <v>5</v>
+      </c>
+      <c r="B10" s="4" t="str">
+        <v>cm.xpt</v>
+      </c>
+      <c r="C10" s="4" t="str">
+        <v>Record</v>
+      </c>
+      <c r="D10" s="4">
         <v>7</v>
       </c>
-      <c r="E3" s="2" t="str">
-        <v>SMENDTC</v>
-      </c>
-      <c r="F3" s="2" t="str">
-        <v>2018-07-18</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="str">
-        <v>se.xpt</v>
-      </c>
-      <c r="C4" s="2" t="str">
+      <c r="E10" s="4" t="str">
+        <v>CMSTDTC</v>
+      </c>
+      <c r="F10" s="4" t="str">
+        <v>2018-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4">
+        <v>5</v>
+      </c>
+      <c r="B11" s="4" t="str">
+        <v>cm.xpt</v>
+      </c>
+      <c r="C11" s="4" t="str">
         <v>Record</v>
       </c>
-      <c r="D4" s="2">
-        <v>5</v>
-      </c>
-      <c r="E4" s="2" t="str">
-        <v>SESTDTC</v>
-      </c>
-      <c r="F4" s="2" t="str">
-        <v>2018-01-24</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2">
-        <v>2</v>
-      </c>
-      <c r="B5" s="2" t="str">
-        <v>se.xpt</v>
-      </c>
-      <c r="C5" s="2" t="str">
-        <v>Record</v>
-      </c>
-      <c r="D5" s="2">
-        <v>5</v>
-      </c>
-      <c r="E5" s="2" t="str">
-        <v>SEENDTC</v>
-      </c>
-      <c r="F5" s="2" t="str">
-        <v>2006-03-10</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2">
-        <v>3</v>
-      </c>
-      <c r="B6" s="2" t="str">
-        <v>sv.xpt</v>
-      </c>
-      <c r="C6" s="2" t="str">
-        <v>Record</v>
-      </c>
-      <c r="D6" s="2">
-        <v>6</v>
-      </c>
-      <c r="E6" s="2" t="str">
-        <v>SVSTDTC</v>
-      </c>
-      <c r="F6" s="2" t="str">
-        <v>2018-02-20T16:38</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2">
-        <v>3</v>
-      </c>
-      <c r="B7" s="2" t="str">
-        <v>sv.xpt</v>
-      </c>
-      <c r="C7" s="2" t="str">
-        <v>Record</v>
-      </c>
-      <c r="D7" s="2">
-        <v>6</v>
-      </c>
-      <c r="E7" s="2" t="str">
-        <v>SVENDTC</v>
-      </c>
-      <c r="F7" s="2" t="str">
-        <v>2018-02-20T16:31:00</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2">
-        <v>4</v>
-      </c>
-      <c r="B8" s="2" t="str">
-        <v>ae.xpt</v>
-      </c>
-      <c r="C8" s="2" t="str">
-        <v>Record</v>
-      </c>
-      <c r="D8" s="2">
-        <v>12</v>
-      </c>
-      <c r="E8" s="2" t="str">
-        <v>AESTDTC</v>
-      </c>
-      <c r="F8" s="2">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2">
-        <v>4</v>
-      </c>
-      <c r="B9" s="2" t="str">
-        <v>ae.xpt</v>
-      </c>
-      <c r="C9" s="2" t="str">
-        <v>Record</v>
-      </c>
-      <c r="D9" s="2">
-        <v>12</v>
-      </c>
-      <c r="E9" s="2" t="str">
-        <v>AEENDTC</v>
-      </c>
-      <c r="F9" s="2" t="str">
-        <v>2018-06-14</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2">
-        <v>5</v>
-      </c>
-      <c r="B10" s="2" t="str">
-        <v>cm.xpt</v>
-      </c>
-      <c r="C10" s="2" t="str">
-        <v>Record</v>
-      </c>
-      <c r="D10" s="2">
+      <c r="D11" s="4">
         <v>7</v>
       </c>
-      <c r="E10" s="2" t="str">
-        <v>CMSTDTC</v>
-      </c>
-      <c r="F10" s="2" t="str">
-        <v>2018-07</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2">
-        <v>5</v>
-      </c>
-      <c r="B11" s="2" t="str">
-        <v>cm.xpt</v>
-      </c>
-      <c r="C11" s="2" t="str">
-        <v>Record</v>
-      </c>
-      <c r="D11" s="2">
-        <v>7</v>
-      </c>
-      <c r="E11" s="2" t="str">
+      <c r="E11" s="4" t="str">
         <v>CMENDTC</v>
       </c>
-      <c r="F11" s="2" t="str">
+      <c r="F11" s="4" t="str">
         <v>2018-06</v>
       </c>
     </row>
@@ -864,258 +856,258 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="str">
+      <c r="A2" s="6" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="5" t="str">
+      <c r="B2" s="6" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="5" t="str">
+      <c r="C2" s="6" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="5" t="str">
+      <c r="D2" s="7" t="str">
         <v>Sequence Number</v>
       </c>
-      <c r="E2" s="5" t="str">
+      <c r="E2" s="7" t="str">
         <v>Disease Milestone Instance Name</v>
       </c>
-      <c r="F2" s="5" t="str">
+      <c r="F2" s="7" t="str">
         <v>Disease Milestone Type</v>
       </c>
-      <c r="G2" s="5" t="str">
+      <c r="G2" s="7" t="str">
         <v>Start Date/Time of Milestone</v>
       </c>
-      <c r="H2" s="5" t="str">
+      <c r="H2" s="7" t="str">
         <v>End Date/Time of Milestone</v>
       </c>
-      <c r="I2" s="5" t="str">
+      <c r="I2" s="7" t="str">
         <v>Study Day of Start of Milestone</v>
       </c>
-      <c r="J2" s="5" t="str">
+      <c r="J2" s="7" t="str">
         <v>Study Day of End of Milestone</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="6" t="str">
+      <c r="A3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="7" t="str">
         <v>Num</v>
       </c>
-      <c r="E3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="6" t="str">
+      <c r="E3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="7" t="str">
         <v>Num</v>
       </c>
-      <c r="J3" s="6" t="str">
+      <c r="J3" s="7" t="str">
         <v>Num</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="7">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="7">
         <v>2</v>
       </c>
-      <c r="C4" s="6" t="str">
+      <c r="C4" s="7" t="str">
         <v>50</v>
       </c>
-      <c r="D4" s="6" t="str">
+      <c r="D4" s="7" t="str">
         <v>8</v>
       </c>
-      <c r="E4" s="6" t="str">
+      <c r="E4" s="7" t="str">
         <v>200</v>
       </c>
-      <c r="F4" s="6" t="str">
+      <c r="F4" s="7" t="str">
         <v>200</v>
       </c>
-      <c r="G4" s="6" t="str">
+      <c r="G4" s="7" t="str">
         <v>19</v>
       </c>
-      <c r="H4" s="6" t="str">
+      <c r="H4" s="7" t="str">
         <v>19</v>
       </c>
-      <c r="I4" s="6" t="str">
+      <c r="I4" s="7" t="str">
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="str">
+      <c r="J4" s="7" t="str">
         <v>8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="str">
+      <c r="A5" s="5" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B5" s="4" t="str">
+      <c r="B5" s="5" t="str">
         <v>SM</v>
       </c>
-      <c r="C5" s="4" t="str">
+      <c r="C5" s="5" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="5">
         <v>1</v>
       </c>
-      <c r="E5" s="4" t="str">
+      <c r="E5" s="5" t="str">
         <v>DIAG</v>
       </c>
-      <c r="F5" s="4" t="str">
+      <c r="F5" s="5" t="str">
         <v>DIAGNOSIS</v>
       </c>
-      <c r="G5" s="4" t="str">
+      <c r="G5" s="5" t="str">
         <v>2018-02-20</v>
       </c>
-      <c r="H5" s="2" t="str">
+      <c r="H5" s="4" t="str">
         <v/>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="5">
         <v>1</v>
       </c>
-      <c r="J5" s="4" t="str">
+      <c r="J5" s="5" t="str">
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="str">
+      <c r="A6" s="5" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B6" s="4" t="str">
+      <c r="B6" s="5" t="str">
         <v>SM</v>
       </c>
-      <c r="C6" s="4" t="str">
+      <c r="C6" s="5" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="5">
         <v>2</v>
       </c>
-      <c r="E6" s="4" t="str">
+      <c r="E6" s="5" t="str">
         <v>HYPO1</v>
       </c>
-      <c r="F6" s="4" t="str">
+      <c r="F6" s="5" t="str">
         <v>HYPOGLYCEMIC EVENT</v>
       </c>
-      <c r="G6" s="4" t="str">
+      <c r="G6" s="5" t="str">
         <v>2018-04-17T09:25</v>
       </c>
-      <c r="H6" s="4" t="str">
+      <c r="H6" s="5" t="str">
         <v>2019-03-13</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="5">
         <v>25</v>
       </c>
-      <c r="J6" s="4" t="str">
+      <c r="J6" s="5" t="str">
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="str">
+      <c r="A7" s="5" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B7" s="4" t="str">
+      <c r="B7" s="5" t="str">
         <v>SM</v>
       </c>
-      <c r="C7" s="4" t="str">
+      <c r="C7" s="5" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="5">
         <v>3</v>
       </c>
-      <c r="E7" s="4" t="str">
+      <c r="E7" s="5" t="str">
         <v>HYPO2</v>
       </c>
-      <c r="F7" s="4" t="str">
+      <c r="F7" s="5" t="str">
         <v>HYPOGLYCEMIC EVENT</v>
       </c>
-      <c r="G7" s="7" t="str">
+      <c r="G7" s="8" t="str">
+        <v>2018-07-18T11:16</v>
+      </c>
+      <c r="H7" s="8" t="str">
         <v>2018-07-18T11:15</v>
       </c>
-      <c r="H7" s="7" t="str">
-        <v>2018-07-18</v>
-      </c>
-      <c r="I7" s="4">
+      <c r="I7" s="5">
         <v>50</v>
       </c>
-      <c r="J7" s="4" t="str">
+      <c r="J7" s="5" t="str">
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="str">
+      <c r="A8" s="5" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B8" s="4" t="str">
+      <c r="B8" s="5" t="str">
         <v>SM</v>
       </c>
-      <c r="C8" s="4" t="str">
+      <c r="C8" s="5" t="str">
         <v>CDISC002</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="5">
         <v>1</v>
       </c>
-      <c r="E8" s="4" t="str">
+      <c r="E8" s="5" t="str">
         <v>DIAG</v>
       </c>
-      <c r="F8" s="4" t="str">
+      <c r="F8" s="5" t="str">
         <v>DIAGNOSIS</v>
       </c>
-      <c r="G8" s="4" t="str">
+      <c r="G8" s="5" t="str">
         <v>2018-03-22</v>
       </c>
-      <c r="H8" s="2" t="str">
+      <c r="H8" s="4" t="str">
         <v/>
       </c>
-      <c r="I8" s="4">
+      <c r="I8" s="5">
         <v>1</v>
       </c>
-      <c r="J8" s="4" t="str">
+      <c r="J8" s="5" t="str">
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="str">
+      <c r="A9" s="5" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B9" s="4" t="str">
+      <c r="B9" s="5" t="str">
         <v>SM</v>
       </c>
-      <c r="C9" s="4" t="str">
+      <c r="C9" s="5" t="str">
         <v>CDISC002</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="5">
         <v>2</v>
       </c>
-      <c r="E9" s="4" t="str">
+      <c r="E9" s="5" t="str">
         <v>HYPO1</v>
       </c>
-      <c r="F9" s="4" t="str">
+      <c r="F9" s="5" t="str">
         <v>HYPOGLYCEMIC EVENT</v>
       </c>
-      <c r="G9" s="4" t="str">
+      <c r="G9" s="5" t="str">
         <v>2018-04-17T09:25</v>
       </c>
-      <c r="H9" s="4" t="str">
+      <c r="H9" s="5" t="str">
         <v>2018-04-17T09</v>
       </c>
-      <c r="I9" s="4">
+      <c r="I9" s="5">
         <v>25</v>
       </c>
-      <c r="J9" s="4" t="str">
+      <c r="J9" s="5" t="str">
         <v/>
       </c>
     </row>
@@ -1169,230 +1161,230 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="str">
+      <c r="A2" s="7" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="6" t="str">
+      <c r="B2" s="7" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="6" t="str">
+      <c r="C2" s="7" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="7" t="str">
         <v>Sequence Number</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="7" t="str">
         <v>Element Code</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="7" t="str">
         <v>Description of Element</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="7" t="str">
         <v>Planned Order of Element within Arm</v>
       </c>
-      <c r="H2" s="6" t="str">
+      <c r="H2" s="7" t="str">
         <v>Epoch</v>
       </c>
-      <c r="I2" s="6" t="str">
+      <c r="I2" s="7" t="str">
         <v>Start Date/Time of Element</v>
       </c>
-      <c r="J2" s="6" t="str">
+      <c r="J2" s="7" t="str">
         <v>End Date/Time of Element</v>
       </c>
-      <c r="K2" s="6" t="str">
+      <c r="K2" s="7" t="str">
         <v>Study Day of Start of Element</v>
       </c>
-      <c r="L2" s="6" t="str">
+      <c r="L2" s="7" t="str">
         <v>Study Day of End of Element</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="6" t="str">
+      <c r="A3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="7" t="str">
         <v>Num</v>
       </c>
-      <c r="E3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="6" t="str">
+      <c r="E3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="7" t="str">
         <v>Num</v>
       </c>
-      <c r="H3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="6" t="str">
+      <c r="H3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="7" t="str">
         <v>Num</v>
       </c>
-      <c r="L3" s="6" t="str">
+      <c r="L3" s="7" t="str">
         <v>Num</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="7">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="7">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="7">
         <v>8</v>
       </c>
-      <c r="D4" s="6" t="str">
+      <c r="D4" s="7" t="str">
         <v>8</v>
       </c>
-      <c r="E4" s="6" t="str">
+      <c r="E4" s="7" t="str">
         <v>8</v>
       </c>
-      <c r="F4" s="6" t="str">
+      <c r="F4" s="7" t="str">
         <v>25</v>
       </c>
-      <c r="G4" s="6" t="str">
+      <c r="G4" s="7" t="str">
         <v>8</v>
       </c>
-      <c r="H4" s="6" t="str">
+      <c r="H4" s="7" t="str">
         <v>25</v>
       </c>
-      <c r="I4" s="6" t="str">
+      <c r="I4" s="7" t="str">
         <v>19</v>
       </c>
-      <c r="J4" s="6" t="str">
+      <c r="J4" s="7" t="str">
         <v>19</v>
       </c>
-      <c r="K4" s="6" t="str">
+      <c r="K4" s="7" t="str">
         <v>8</v>
       </c>
-      <c r="L4" s="6" t="str">
+      <c r="L4" s="7" t="str">
         <v>8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="str">
+      <c r="A5" s="5" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B5" s="4" t="str">
+      <c r="B5" s="5" t="str">
         <v>SE</v>
       </c>
-      <c r="C5" s="4" t="str">
+      <c r="C5" s="5" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="5">
         <v>1</v>
       </c>
-      <c r="E5" s="4" t="str">
+      <c r="E5" s="5" t="str">
         <v>SCRN</v>
       </c>
-      <c r="F5" s="4" t="str">
+      <c r="F5" s="5" t="str">
         <v>Screen</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="5">
         <v>1</v>
       </c>
-      <c r="H5" s="4" t="str">
+      <c r="H5" s="5" t="str">
         <v>SCREENING</v>
       </c>
-      <c r="I5" s="7" t="str">
+      <c r="I5" s="8" t="str">
         <v>2018-01-24</v>
       </c>
-      <c r="J5" s="7" t="str">
+      <c r="J5" s="9" t="str">
         <v>2006-03-10</v>
       </c>
-      <c r="K5" s="4" t="str">
+      <c r="K5" s="5" t="str">
         <v>-27</v>
       </c>
-      <c r="L5" s="4" t="str">
+      <c r="L5" s="5" t="str">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="str">
+      <c r="A6" s="5" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B6" s="4" t="str">
+      <c r="B6" s="5" t="str">
         <v>SE</v>
       </c>
-      <c r="C6" s="4" t="str">
+      <c r="C6" s="5" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="5">
         <v>2</v>
       </c>
-      <c r="E6" s="4" t="str">
+      <c r="E6" s="5" t="str">
         <v>IKD</v>
       </c>
-      <c r="F6" s="4" t="str">
+      <c r="F6" s="5" t="str">
         <v>Treatment IKD</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="5">
         <v>2</v>
       </c>
-      <c r="H6" s="4" t="str">
+      <c r="H6" s="5" t="str">
         <v>TREATMENT</v>
       </c>
-      <c r="I6" s="4" t="str">
+      <c r="I6" s="5" t="str">
         <v>2018-12-20T09:40</v>
       </c>
-      <c r="J6" s="4" t="str">
+      <c r="J6" s="5" t="str">
         <v>2019-03-22T10:38</v>
       </c>
-      <c r="K6" s="4" t="str">
+      <c r="K6" s="5" t="str">
         <v>1</v>
       </c>
-      <c r="L6" s="4" t="str">
+      <c r="L6" s="5" t="str">
         <v>396</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="str">
+      <c r="A7" s="5" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B7" s="4" t="str">
+      <c r="B7" s="5" t="str">
         <v>SE</v>
       </c>
-      <c r="C7" s="4" t="str">
+      <c r="C7" s="5" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="5">
         <v>3</v>
       </c>
-      <c r="E7" s="4" t="str">
+      <c r="E7" s="5" t="str">
         <v>FU</v>
       </c>
-      <c r="F7" s="4" t="str">
+      <c r="F7" s="5" t="str">
         <v>Follow-up</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="5">
         <v>3</v>
       </c>
-      <c r="H7" s="4" t="str">
+      <c r="H7" s="5" t="str">
         <v>FOLLOW-UP</v>
       </c>
-      <c r="I7" s="4" t="str">
+      <c r="I7" s="5" t="str">
         <v>2019-03-22</v>
       </c>
-      <c r="J7" s="4" t="str">
+      <c r="J7" s="5" t="str">
         <v>2019-03-22T10:38</v>
       </c>
-      <c r="K7" s="4" t="str">
+      <c r="K7" s="5" t="str">
         <v>396</v>
       </c>
-      <c r="L7" s="4" t="str">
+      <c r="L7" s="5" t="str">
         <v>1430</v>
       </c>
     </row>
@@ -1443,212 +1435,212 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="str">
+      <c r="A2" s="7" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="6" t="str">
+      <c r="B2" s="7" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="6" t="str">
+      <c r="C2" s="7" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="7" t="str">
         <v>Visit Number</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="7" t="str">
         <v>Visit Name</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="7" t="str">
         <v>Planned Study Day of Visit</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="7" t="str">
         <v>Subject Reference Start Date/Time</v>
       </c>
-      <c r="H2" s="6" t="str">
+      <c r="H2" s="7" t="str">
         <v>Start Date/Time of Observation</v>
       </c>
-      <c r="I2" s="6" t="str">
+      <c r="I2" s="7" t="str">
         <v>Study Day of Start of Observation</v>
       </c>
-      <c r="J2" s="6" t="str">
+      <c r="J2" s="7" t="str">
         <v>End Date/Time of Observation</v>
       </c>
-      <c r="K2" s="6" t="str">
+      <c r="K2" s="7" t="str">
         <v>Study Day of End of Observation</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="6" t="str">
+      <c r="A3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="7" t="str">
         <v>Num</v>
       </c>
-      <c r="E3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="6" t="str">
+      <c r="E3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="7" t="str">
         <v>Num</v>
       </c>
-      <c r="G3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="6" t="str">
+      <c r="G3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="7" t="str">
         <v>Num</v>
       </c>
-      <c r="J3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="6" t="str">
+      <c r="J3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="7" t="str">
         <v>Num</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="7">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="7">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="7">
         <v>8</v>
       </c>
-      <c r="D4" s="6" t="str">
+      <c r="D4" s="7" t="str">
         <v>8</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="7">
         <v>10</v>
       </c>
-      <c r="F4" s="6" t="str">
+      <c r="F4" s="7" t="str">
         <v>8</v>
       </c>
-      <c r="G4" s="6" t="str">
+      <c r="G4" s="7" t="str">
         <v>25</v>
       </c>
-      <c r="H4" s="6" t="str">
+      <c r="H4" s="7" t="str">
         <v>19</v>
       </c>
-      <c r="I4" s="6" t="str">
+      <c r="I4" s="7" t="str">
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="str">
+      <c r="J4" s="7" t="str">
         <v>19</v>
       </c>
-      <c r="K4" s="6" t="str">
+      <c r="K4" s="7" t="str">
         <v>8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="str">
+      <c r="A5" s="5" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B5" s="4" t="str">
+      <c r="B5" s="5" t="str">
         <v>SV</v>
       </c>
-      <c r="C5" s="4" t="str">
+      <c r="C5" s="5" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D5" s="4" t="str">
+      <c r="D5" s="5" t="str">
         <v>0</v>
       </c>
-      <c r="E5" s="4" t="str">
+      <c r="E5" s="5" t="str">
         <v>SCREENING</v>
       </c>
-      <c r="F5" s="4" t="str">
+      <c r="F5" s="5" t="str">
         <v>-21</v>
       </c>
-      <c r="G5" s="4" t="str">
+      <c r="G5" s="5" t="str">
         <v>SCREENING</v>
       </c>
-      <c r="H5" s="4" t="str">
+      <c r="H5" s="5" t="str">
         <v>2018-01-24</v>
       </c>
-      <c r="I5" s="4" t="str">
+      <c r="I5" s="5" t="str">
         <v>-27</v>
       </c>
-      <c r="J5" s="4" t="str">
+      <c r="J5" s="5" t="str">
         <v>2018-02-20</v>
       </c>
-      <c r="K5" s="4" t="str">
+      <c r="K5" s="5" t="str">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="str">
+      <c r="A6" s="5" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B6" s="4" t="str">
+      <c r="B6" s="5" t="str">
         <v>SV</v>
       </c>
-      <c r="C6" s="4" t="str">
+      <c r="C6" s="5" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D6" s="4" t="str">
+      <c r="D6" s="5" t="str">
         <v>110</v>
       </c>
-      <c r="E6" s="4" t="str">
+      <c r="E6" s="5" t="str">
         <v>CYCLE 1 DAY 1</v>
       </c>
-      <c r="F6" s="4" t="str">
+      <c r="F6" s="5" t="str">
         <v>1</v>
       </c>
-      <c r="G6" s="4" t="str">
+      <c r="G6" s="5" t="str">
         <v>SCREENING</v>
       </c>
-      <c r="H6" s="7" t="str">
+      <c r="H6" s="9" t="str">
         <v>2018-02-20T16:38</v>
       </c>
-      <c r="I6" s="4" t="str">
+      <c r="I6" s="5" t="str">
         <v>-5</v>
       </c>
-      <c r="J6" s="7" t="str">
+      <c r="J6" s="9" t="str">
         <v>2018-02-20T16:31:00</v>
       </c>
-      <c r="K6" s="4" t="str">
+      <c r="K6" s="5" t="str">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="str">
+      <c r="A7" s="5" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B7" s="4" t="str">
+      <c r="B7" s="5" t="str">
         <v>SV</v>
       </c>
-      <c r="C7" s="4" t="str">
+      <c r="C7" s="5" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D7" s="4" t="str">
+      <c r="D7" s="5" t="str">
         <v>120</v>
       </c>
-      <c r="E7" s="4" t="str">
+      <c r="E7" s="5" t="str">
         <v>CYCLE 1 DAY 2</v>
       </c>
-      <c r="F7" s="4" t="str">
+      <c r="F7" s="5" t="str">
         <v>2</v>
       </c>
-      <c r="G7" s="4" t="str">
+      <c r="G7" s="5" t="str">
         <v>TREATMENT</v>
       </c>
-      <c r="H7" s="4" t="str">
+      <c r="H7" s="5" t="str">
         <v>2018-02-21</v>
       </c>
-      <c r="I7" s="4" t="str">
+      <c r="I7" s="5" t="str">
         <v>2</v>
       </c>
-      <c r="J7" s="4" t="str">
+      <c r="J7" s="5" t="str">
         <v>2018-02-21T12:05</v>
       </c>
-      <c r="K7" s="4" t="str">
+      <c r="K7" s="5" t="str">
         <v>2</v>
       </c>
     </row>
@@ -1696,354 +1688,354 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="str">
+      <c r="A2" s="7" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="6" t="str">
+      <c r="B2" s="7" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="6" t="str">
+      <c r="C2" s="7" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="7" t="str">
         <v>Reported Term for the Adverse Event</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="7" t="str">
         <v>Serious Event</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="7" t="str">
         <v>Outcome of Adverse Event</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="7" t="str">
         <v>Start Date/Time of Adverse Event</v>
       </c>
-      <c r="H2" s="6" t="str">
+      <c r="H2" s="7" t="str">
         <v>Study Day of Start of Observation</v>
       </c>
-      <c r="I2" s="6" t="str">
+      <c r="I2" s="7" t="str">
         <v>End Date/Time of Adverse Event</v>
       </c>
-      <c r="J2" s="6" t="str">
+      <c r="J2" s="7" t="str">
         <v>Study Day of End of Observation</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="6" t="str">
+      <c r="A3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="7" t="str">
         <v>Num</v>
       </c>
-      <c r="I3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="6" t="str">
+      <c r="I3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="J3" s="7" t="str">
         <v>Num</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="7">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="7">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="7">
         <v>8</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="7">
         <v>40</v>
       </c>
-      <c r="E4" s="6" t="str">
+      <c r="E4" s="7" t="str">
         <v>1</v>
       </c>
-      <c r="F4" s="6" t="str">
+      <c r="F4" s="7" t="str">
         <v>40</v>
       </c>
-      <c r="G4" s="6" t="str">
+      <c r="G4" s="7" t="str">
         <v>19</v>
       </c>
-      <c r="H4" s="6" t="str">
+      <c r="H4" s="7" t="str">
         <v>8</v>
       </c>
-      <c r="I4" s="6" t="str">
+      <c r="I4" s="7" t="str">
         <v>19</v>
       </c>
-      <c r="J4" s="6" t="str">
+      <c r="J4" s="7" t="str">
         <v>8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="str">
+      <c r="A5" s="4" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B5" s="4" t="str">
+      <c r="B5" s="5" t="str">
         <v>AE</v>
       </c>
-      <c r="C5" s="8" t="str">
+      <c r="C5" s="4" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D5" s="4" t="str">
+      <c r="D5" s="5" t="str">
         <v>INFUSION ASSOCIATE REACTION</v>
       </c>
-      <c r="E5" s="4" t="str">
+      <c r="E5" s="5" t="str">
         <v>N</v>
       </c>
-      <c r="F5" s="4" t="str">
+      <c r="F5" s="5" t="str">
         <v>RECOVERED/RESOLVED</v>
       </c>
-      <c r="G5" s="4" t="str">
+      <c r="G5" s="5" t="str">
         <v>2018-02-20</v>
       </c>
-      <c r="H5" s="4" t="str">
+      <c r="H5" s="5" t="str">
         <v>1</v>
       </c>
-      <c r="I5" s="4" t="str">
+      <c r="I5" s="5" t="str">
         <v>2018-02-20</v>
       </c>
-      <c r="J5" s="4" t="str">
+      <c r="J5" s="5" t="str">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="str">
+      <c r="A6" s="4" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B6" s="4" t="str">
+      <c r="B6" s="5" t="str">
         <v>AE</v>
       </c>
-      <c r="C6" s="8" t="str">
+      <c r="C6" s="4" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D6" s="4" t="str">
+      <c r="D6" s="5" t="str">
         <v>INSOMNIA</v>
       </c>
-      <c r="E6" s="4" t="str">
+      <c r="E6" s="5" t="str">
         <v>N</v>
       </c>
-      <c r="F6" s="4" t="str">
+      <c r="F6" s="5" t="str">
         <v>RECOVERED/RESOLVED</v>
       </c>
-      <c r="G6" s="4" t="str">
+      <c r="G6" s="5" t="str">
         <v>2018-02-22</v>
       </c>
-      <c r="H6" s="4" t="str">
+      <c r="H6" s="5" t="str">
         <v>3</v>
       </c>
-      <c r="I6" s="4" t="str">
+      <c r="I6" s="5" t="str">
         <v>2018-10-30</v>
       </c>
-      <c r="J6" s="4" t="str">
+      <c r="J6" s="5" t="str">
         <v>253</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="str">
+      <c r="A7" s="4" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B7" s="4" t="str">
+      <c r="B7" s="5" t="str">
         <v>AE</v>
       </c>
-      <c r="C7" s="8" t="str">
+      <c r="C7" s="4" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D7" s="4" t="str">
+      <c r="D7" s="5" t="str">
         <v>LETHARGY</v>
       </c>
-      <c r="E7" s="4" t="str">
+      <c r="E7" s="5" t="str">
         <v>N</v>
       </c>
-      <c r="F7" s="4" t="str">
+      <c r="F7" s="5" t="str">
         <v>RECOVERED/RESOLVED</v>
       </c>
-      <c r="G7" s="4" t="str">
+      <c r="G7" s="5" t="str">
         <v>2018-02-22</v>
       </c>
-      <c r="H7" s="4" t="str">
+      <c r="H7" s="5" t="str">
         <v>3</v>
       </c>
-      <c r="I7" s="4" t="str">
+      <c r="I7" s="5" t="str">
         <v>2018-06-12</v>
       </c>
-      <c r="J7" s="4" t="str">
+      <c r="J7" s="5" t="str">
         <v>113</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="str">
+      <c r="A8" s="4" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B8" s="4" t="str">
+      <c r="B8" s="5" t="str">
         <v>AE</v>
       </c>
-      <c r="C8" s="8" t="str">
+      <c r="C8" s="4" t="str">
         <v>CDISC002</v>
       </c>
-      <c r="D8" s="4" t="str">
+      <c r="D8" s="5" t="str">
         <v>LEFT HIP PAIN CAUSE UNKNOWN</v>
       </c>
-      <c r="E8" s="4" t="str">
+      <c r="E8" s="5" t="str">
         <v>N</v>
       </c>
-      <c r="F8" s="4" t="str">
+      <c r="F8" s="5" t="str">
         <v>RECOVERED/RESOLVED</v>
       </c>
-      <c r="G8" s="4" t="str">
+      <c r="G8" s="5" t="str">
         <v>2018-04-16</v>
       </c>
-      <c r="H8" s="4" t="str">
+      <c r="H8" s="5" t="str">
         <v>-1</v>
       </c>
-      <c r="I8" s="4" t="str">
+      <c r="I8" s="5" t="str">
         <v>2018-04-23</v>
       </c>
-      <c r="J8" s="4" t="str">
+      <c r="J8" s="5" t="str">
         <v>7</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="str">
+      <c r="A9" s="4" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B9" s="4" t="str">
+      <c r="B9" s="5" t="str">
         <v>AE</v>
       </c>
-      <c r="C9" s="8" t="str">
+      <c r="C9" s="4" t="str">
         <v>CDISC002</v>
       </c>
-      <c r="D9" s="4" t="str">
+      <c r="D9" s="5" t="str">
         <v>FATIGUE</v>
       </c>
-      <c r="E9" s="4" t="str">
+      <c r="E9" s="5" t="str">
         <v>N</v>
       </c>
-      <c r="F9" s="4" t="str">
+      <c r="F9" s="5" t="str">
         <v>RECOVERED/RESOLVED</v>
       </c>
-      <c r="G9" s="4" t="str">
+      <c r="G9" s="5" t="str">
         <v>2018-05-02</v>
       </c>
-      <c r="H9" s="4" t="str">
+      <c r="H9" s="5" t="str">
         <v>16</v>
       </c>
-      <c r="I9" s="4" t="str">
+      <c r="I9" s="5" t="str">
         <v>2019-03</v>
       </c>
-      <c r="J9" s="4" t="str">
+      <c r="J9" s="5" t="str">
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="str">
+      <c r="A10" s="4" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B10" s="4" t="str">
+      <c r="B10" s="5" t="str">
         <v>AE</v>
       </c>
-      <c r="C10" s="8" t="str">
+      <c r="C10" s="4" t="str">
         <v>CDISC003</v>
       </c>
-      <c r="D10" s="4" t="str">
+      <c r="D10" s="5" t="str">
         <v>CALF PAIN</v>
       </c>
-      <c r="E10" s="4" t="str">
+      <c r="E10" s="5" t="str">
         <v>N</v>
       </c>
-      <c r="F10" s="4" t="str">
+      <c r="F10" s="5" t="str">
         <v>NOT RECOVERED/NOT RESOLVED</v>
       </c>
-      <c r="G10" s="4" t="str">
+      <c r="G10" s="5" t="str">
         <v>2018-07-10</v>
       </c>
-      <c r="H10" s="4" t="str">
+      <c r="H10" s="5" t="str">
         <v>84</v>
       </c>
-      <c r="I10" s="4" t="str">
+      <c r="I10" s="5" t="str">
         <v/>
       </c>
-      <c r="J10" s="4" t="str">
+      <c r="J10" s="5" t="str">
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="str">
+      <c r="A11" s="4" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B11" s="4" t="str">
+      <c r="B11" s="5" t="str">
         <v>AE</v>
       </c>
-      <c r="C11" s="8" t="str">
+      <c r="C11" s="4" t="str">
         <v>CDISC003</v>
       </c>
-      <c r="D11" s="4" t="str">
+      <c r="D11" s="5" t="str">
         <v>DELIRIUM</v>
       </c>
-      <c r="E11" s="4" t="str">
+      <c r="E11" s="5" t="str">
         <v>N</v>
       </c>
-      <c r="F11" s="4" t="str">
+      <c r="F11" s="5" t="str">
         <v>RECOVERED/RESOLVED</v>
       </c>
-      <c r="G11" s="8" t="str">
+      <c r="G11" s="4" t="str">
         <v>2018-06</v>
       </c>
-      <c r="H11" s="4" t="str">
+      <c r="H11" s="5" t="str">
         <v>2</v>
       </c>
-      <c r="I11" s="4" t="str">
+      <c r="I11" s="5" t="str">
         <v>2018-06-14</v>
       </c>
-      <c r="J11" s="4" t="str">
+      <c r="J11" s="5" t="str">
         <v>29</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="str">
+      <c r="A12" s="4" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B12" s="4" t="str">
+      <c r="B12" s="5" t="str">
         <v>AE</v>
       </c>
-      <c r="C12" s="8" t="str">
+      <c r="C12" s="4" t="str">
         <v>CDISC003</v>
       </c>
-      <c r="D12" s="4" t="str">
+      <c r="D12" s="5" t="str">
         <v>DRY COUGH</v>
       </c>
-      <c r="E12" s="4" t="str">
+      <c r="E12" s="5" t="str">
         <v>N</v>
       </c>
-      <c r="F12" s="4" t="str">
+      <c r="F12" s="5" t="str">
         <v>RECOVERED/RESOLVED</v>
       </c>
-      <c r="G12" s="9" t="str">
+      <c r="G12" s="10" t="str">
         <v>2019</v>
       </c>
-      <c r="H12" s="4" t="str">
+      <c r="H12" s="5" t="str">
         <v>2</v>
       </c>
-      <c r="I12" s="7" t="str">
+      <c r="I12" s="9" t="str">
         <v>2018-06-14</v>
       </c>
-      <c r="J12" s="4" t="str">
+      <c r="J12" s="5" t="str">
         <v>29</v>
       </c>
     </row>
@@ -2094,207 +2086,207 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="str">
+      <c r="A2" s="7" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="6" t="str">
+      <c r="B2" s="7" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="6" t="str">
+      <c r="C2" s="7" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="7" t="str">
         <v>Sequence Number</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="7" t="str">
         <v>Reported Name of Drug, Med, or Therapy</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="F2" s="7" t="str">
         <v>Standardized Medication Name</v>
       </c>
-      <c r="G2" s="6" t="str">
+      <c r="G2" s="7" t="str">
         <v>Category for Medication</v>
       </c>
-      <c r="H2" s="6" t="str">
+      <c r="H2" s="7" t="str">
         <v>Start Date/Time of Medication</v>
       </c>
-      <c r="I2" s="6" t="str">
+      <c r="I2" s="7" t="str">
         <v>Study Day of Start of Medication</v>
       </c>
-      <c r="J2" s="6" t="str">
+      <c r="J2" s="7" t="str">
         <v>End Date/Time of Medication</v>
       </c>
-      <c r="K2" s="6" t="str">
+      <c r="K2" s="7" t="str">
         <v>Study Day of End of Medication</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="6" t="str">
+      <c r="A3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="7" t="str">
         <v>Num</v>
       </c>
-      <c r="E3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="F3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="6" t="str">
+      <c r="E3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="H3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="I3" s="7" t="str">
         <v>Num</v>
       </c>
-      <c r="J3" s="6" t="str">
-        <v>Char</v>
-      </c>
-      <c r="K3" s="6" t="str">
+      <c r="J3" s="7" t="str">
+        <v>Char</v>
+      </c>
+      <c r="K3" s="7" t="str">
         <v>Num</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="7">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="7">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="7">
         <v>8</v>
       </c>
-      <c r="D4" s="6" t="str">
+      <c r="D4" s="7" t="str">
         <v>8</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="7">
         <v>200</v>
       </c>
-      <c r="F4" s="6" t="str">
+      <c r="F4" s="7" t="str">
         <v>200</v>
       </c>
-      <c r="G4" s="6" t="str">
+      <c r="G4" s="7" t="str">
         <v>50</v>
       </c>
-      <c r="H4" s="6" t="str">
+      <c r="H4" s="7" t="str">
         <v>19</v>
       </c>
-      <c r="I4" s="6" t="str">
+      <c r="I4" s="7" t="str">
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="str">
+      <c r="J4" s="7" t="str">
         <v>19</v>
       </c>
-      <c r="K4" s="6" t="str">
+      <c r="K4" s="7" t="str">
         <v>8</v>
       </c>
     </row>
     <row r="5" xml:space="preserve">
-      <c r="A5" s="8" t="str">
+      <c r="A5" s="4" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B5" s="4" t="str">
+      <c r="B5" s="5" t="str">
         <v>CM</v>
       </c>
-      <c r="C5" s="8" t="str">
+      <c r="C5" s="4" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D5" s="8" t="str">
+      <c r="D5" s="4" t="str">
         <v>1</v>
       </c>
-      <c r="E5" s="2" t="str">
+      <c r="E5" s="4" t="str">
         <v>VALACICLOVIR 500 MG</v>
       </c>
-      <c r="F5" s="4" t="str" xml:space="preserve">
+      <c r="F5" s="5" t="str" xml:space="preserve">
         <v xml:space="preserve">CMDECOD
 VALACICLOVIR</v>
       </c>
-      <c r="G5" s="2" t="str">
+      <c r="G5" s="4" t="str">
         <v>MEDICATION</v>
       </c>
-      <c r="H5" s="4" t="str">
+      <c r="H5" s="5" t="str">
         <v>2018-02-20</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="str">
+      <c r="A6" s="4" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B6" s="4" t="str">
+      <c r="B6" s="5" t="str">
         <v>CM</v>
       </c>
-      <c r="C6" s="8" t="str">
+      <c r="C6" s="4" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D6" s="8" t="str">
+      <c r="D6" s="4" t="str">
         <v>2</v>
       </c>
-      <c r="E6" s="2" t="str">
+      <c r="E6" s="4" t="str">
         <v>G-CSF 480 MCG</v>
       </c>
-      <c r="F6" s="4" t="str">
+      <c r="F6" s="5" t="str">
         <v>CMDECOD GRANULOCYTE COLONY STIMULATING FACTOR</v>
       </c>
-      <c r="G6" s="2" t="str">
+      <c r="G6" s="4" t="str">
         <v>MEDICATION</v>
       </c>
-      <c r="H6" s="4" t="str">
+      <c r="H6" s="5" t="str">
         <v>2018-02-27</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="4">
         <v>8</v>
       </c>
-      <c r="J6" s="4" t="str">
+      <c r="J6" s="5" t="str">
         <v>2018-03-03</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="str">
+      <c r="A7" s="4" t="str">
         <v>CDISCPILOT01</v>
       </c>
-      <c r="B7" s="4" t="str">
+      <c r="B7" s="5" t="str">
         <v>CM</v>
       </c>
-      <c r="C7" s="8" t="str">
+      <c r="C7" s="4" t="str">
         <v>CDISC001</v>
       </c>
-      <c r="D7" s="8" t="str">
+      <c r="D7" s="4" t="str">
         <v>3</v>
       </c>
-      <c r="E7" s="4" t="str">
+      <c r="E7" s="5" t="str">
         <v>CIPROFLOXACIN 500 MG</v>
       </c>
-      <c r="F7" s="4" t="str">
+      <c r="F7" s="5" t="str">
         <v>CIPROFLOXACIN</v>
       </c>
-      <c r="G7" s="4" t="str">
+      <c r="G7" s="5" t="str">
         <v>MEDICATION</v>
       </c>
       <c r="H7" s="10" t="str">
         <v>2018-07</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="4">
         <v>45</v>
       </c>
       <c r="J7" s="11" t="str">
         <v>2018-06</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7" s="4">
         <v>88</v>
       </c>
     </row>

--- a/rules/CORE-000718/negative/01/data/unit-test-coreid-FB3209-negative.xlsx
+++ b/rules/CORE-000718/negative/01/data/unit-test-coreid-FB3209-negative.xlsx
@@ -598,7 +598,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F9"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="str">
@@ -625,19 +625,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="str">
-        <v>sm.xpt</v>
+        <v>se.xpt</v>
       </c>
       <c r="C2" s="2" t="str">
         <v>Record</v>
       </c>
       <c r="D2" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2" s="2" t="str">
-        <v>SMSTDTC</v>
+        <v>SESTDTC</v>
       </c>
       <c r="F2" s="2" t="str">
-        <v>2018-07-18T11:15</v>
+        <v>2018-01-24</v>
       </c>
     </row>
     <row r="3">
@@ -645,19 +645,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="str">
-        <v>sm.xpt</v>
+        <v>se.xpt</v>
       </c>
       <c r="C3" s="2" t="str">
         <v>Record</v>
       </c>
       <c r="D3" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E3" s="2" t="str">
-        <v>SMENDTC</v>
+        <v>SEENDTC</v>
       </c>
       <c r="F3" s="2" t="str">
-        <v>2018-07-18</v>
+        <v>2006-03-10</v>
       </c>
     </row>
     <row r="4">
@@ -665,19 +665,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="str">
-        <v>se.xpt</v>
+        <v>sv.xpt</v>
       </c>
       <c r="C4" s="2" t="str">
         <v>Record</v>
       </c>
       <c r="D4" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" s="2" t="str">
-        <v>SESTDTC</v>
+        <v>SVSTDTC</v>
       </c>
       <c r="F4" s="2" t="str">
-        <v>2018-01-24</v>
+        <v>2018-02-20T16:38</v>
       </c>
     </row>
     <row r="5">
@@ -685,19 +685,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="str">
-        <v>se.xpt</v>
+        <v>sv.xpt</v>
       </c>
       <c r="C5" s="2" t="str">
         <v>Record</v>
       </c>
       <c r="D5" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" s="2" t="str">
-        <v>SEENDTC</v>
+        <v>SVENDTC</v>
       </c>
       <c r="F5" s="2" t="str">
-        <v>2006-03-10</v>
+        <v>2018-02-20T16:31:00</v>
       </c>
     </row>
     <row r="6">
@@ -705,19 +705,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="str">
-        <v>sv.xpt</v>
+        <v>ae.xpt</v>
       </c>
       <c r="C6" s="2" t="str">
         <v>Record</v>
       </c>
       <c r="D6" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E6" s="2" t="str">
-        <v>SVSTDTC</v>
-      </c>
-      <c r="F6" s="2" t="str">
-        <v>2018-02-20T16:38</v>
+        <v>AESTDTC</v>
+      </c>
+      <c r="F6" s="2">
+        <v>2019</v>
       </c>
     </row>
     <row r="7">
@@ -725,19 +725,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="str">
-        <v>sv.xpt</v>
+        <v>ae.xpt</v>
       </c>
       <c r="C7" s="2" t="str">
         <v>Record</v>
       </c>
       <c r="D7" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E7" s="2" t="str">
-        <v>SVENDTC</v>
+        <v>AEENDTC</v>
       </c>
       <c r="F7" s="2" t="str">
-        <v>2018-02-20T16:31:00</v>
+        <v>2018-06-14</v>
       </c>
     </row>
     <row r="8">
@@ -745,19 +745,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="str">
-        <v>ae.xpt</v>
+        <v>cm.xpt</v>
       </c>
       <c r="C8" s="2" t="str">
         <v>Record</v>
       </c>
       <c r="D8" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E8" s="2" t="str">
-        <v>AESTDTC</v>
-      </c>
-      <c r="F8" s="2">
-        <v>2019</v>
+        <v>CMSTDTC</v>
+      </c>
+      <c r="F8" s="2" t="str">
+        <v>2018-07</v>
       </c>
     </row>
     <row r="9">
@@ -765,58 +765,18 @@
         <v>4</v>
       </c>
       <c r="B9" s="2" t="str">
-        <v>ae.xpt</v>
+        <v>cm.xpt</v>
       </c>
       <c r="C9" s="2" t="str">
         <v>Record</v>
       </c>
       <c r="D9" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E9" s="2" t="str">
-        <v>AEENDTC</v>
+        <v>CMENDTC</v>
       </c>
       <c r="F9" s="2" t="str">
-        <v>2018-06-14</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2">
-        <v>5</v>
-      </c>
-      <c r="B10" s="2" t="str">
-        <v>cm.xpt</v>
-      </c>
-      <c r="C10" s="2" t="str">
-        <v>Record</v>
-      </c>
-      <c r="D10" s="2">
-        <v>7</v>
-      </c>
-      <c r="E10" s="2" t="str">
-        <v>CMSTDTC</v>
-      </c>
-      <c r="F10" s="2" t="str">
-        <v>2018-07</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2">
-        <v>5</v>
-      </c>
-      <c r="B11" s="2" t="str">
-        <v>cm.xpt</v>
-      </c>
-      <c r="C11" s="2" t="str">
-        <v>Record</v>
-      </c>
-      <c r="D11" s="2">
-        <v>7</v>
-      </c>
-      <c r="E11" s="2" t="str">
-        <v>CMENDTC</v>
-      </c>
-      <c r="F11" s="2" t="str">
         <v>2018-06</v>
       </c>
     </row>
@@ -1042,10 +1002,10 @@
       <c r="F7" s="4" t="str">
         <v>HYPOGLYCEMIC EVENT</v>
       </c>
-      <c r="G7" s="7" t="str">
+      <c r="G7" t="str" s="4">
         <v>2018-07-18T11:15</v>
       </c>
-      <c r="H7" s="7" t="str">
+      <c r="H7" t="str" s="4">
         <v>2018-07-18</v>
       </c>
       <c r="I7" s="4">
